--- a/tools/importer/reports/import-content-page.report.xlsx
+++ b/tools/importer/reports/import-content-page.report.xlsx
@@ -52,7 +52,7 @@
     <t>content-page</t>
   </si>
   <si>
-    <t>2026-09-23T18:52:30.654Z</t>
+    <t>2026-09-24T07:36:21.095Z</t>
   </si>
   <si>
     <t>Home - Pet Care Network | Destination Pet</t>

--- a/tools/importer/reports/import-content-page.report.xlsx
+++ b/tools/importer/reports/import-content-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,13 +52,61 @@
     <t>content-page</t>
   </si>
   <si>
-    <t>2026-09-24T07:36:21.095Z</t>
+    <t>2026-09-24T08:14:37.339Z</t>
   </si>
   <si>
     <t>Home - Pet Care Network | Destination Pet</t>
   </si>
   <si>
     <t>https://www.destinationpet.com/</t>
+  </si>
+  <si>
+    <t>live-webinar.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark"]</t>
+  </si>
+  <si>
+    <t>live-webinar</t>
+  </si>
+  <si>
+    <t>2026-09-24T08:14:41.531Z</t>
+  </si>
+  <si>
+    <t>A Series of Webinars | Destination Pet</t>
+  </si>
+  <si>
+    <t>https://www.destinationpet.com/live-webinar/</t>
+  </si>
+  <si>
+    <t>live-webinar/webinar-redirect.report.json</t>
+  </si>
+  <si>
+    <t>live-webinar/webinar-redirect</t>
+  </si>
+  <si>
+    <t>2026-09-24T08:14:45.556Z</t>
+  </si>
+  <si>
+    <t>Webinar Redirect - Destination Pet</t>
+  </si>
+  <si>
+    <t>https://www.destinationpet.com/live-webinar/webinar-redirect/</t>
+  </si>
+  <si>
+    <t>live-webinar/webinars-for-pet.report.json</t>
+  </si>
+  <si>
+    <t>live-webinar/webinars-for-pet</t>
+  </si>
+  <si>
+    <t>2026-09-24T08:14:49.609Z</t>
+  </si>
+  <si>
+    <t>Webinars for Pet - Destination Pet</t>
+  </si>
+  <si>
+    <t>https://www.destinationpet.com/live-webinar/webinars-for-pet/</t>
   </si>
 </sst>
 </file>
@@ -447,16 +495,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="7" width="43" customWidth="1"/>
-    <col min="8" max="8" width="33" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -509,6 +557,84 @@
       </c>
       <c r="H2" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-content-page.report.xlsx
+++ b/tools/importer/reports/import-content-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
   <si>
     <t>_reportFile</t>
   </si>
@@ -40,7 +40,7 @@
     <t>index.report.json</t>
   </si>
   <si>
-    <t>["hero-minimal-dark","columns-comfortable-light","cards","columns-minimal-light","quote"]</t>
+    <t>["hero-minimal-dark","columns-comfortable-light","cards","columns-minimal-light","quote","quote"]</t>
   </si>
   <si>
     <t>index</t>
@@ -52,7 +52,7 @@
     <t>content-page</t>
   </si>
   <si>
-    <t>2026-09-24T08:14:37.339Z</t>
+    <t>2026-09-24T08:51:22.936Z</t>
   </si>
   <si>
     <t>Home - Pet Care Network | Destination Pet</t>
@@ -64,22 +64,25 @@
     <t>live-webinar.report.json</t>
   </si>
   <si>
+    <t>["hero-minimal-dark","quote"]</t>
+  </si>
+  <si>
+    <t>live-webinar</t>
+  </si>
+  <si>
+    <t>2026-09-24T08:51:27.088Z</t>
+  </si>
+  <si>
+    <t>A Series of Webinars | Destination Pet</t>
+  </si>
+  <si>
+    <t>https://www.destinationpet.com/live-webinar/</t>
+  </si>
+  <si>
+    <t>live-webinar/webinar-redirect.report.json</t>
+  </si>
+  <si>
     <t>["hero-minimal-dark"]</t>
-  </si>
-  <si>
-    <t>live-webinar</t>
-  </si>
-  <si>
-    <t>2026-09-24T08:14:41.531Z</t>
-  </si>
-  <si>
-    <t>A Series of Webinars | Destination Pet</t>
-  </si>
-  <si>
-    <t>https://www.destinationpet.com/live-webinar/</t>
-  </si>
-  <si>
-    <t>live-webinar/webinar-redirect.report.json</t>
   </si>
   <si>
     <t>live-webinar/webinar-redirect</t>
@@ -590,10 +593,10 @@
         <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -602,24 +605,24 @@
         <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -628,13 +631,13 @@
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-content-page.report.xlsx
+++ b/tools/importer/reports/import-content-page.report.xlsx
@@ -52,7 +52,7 @@
     <t>content-page</t>
   </si>
   <si>
-    <t>2026-09-24T08:51:22.936Z</t>
+    <t>2026-09-24T12:08:41.569Z</t>
   </si>
   <si>
     <t>Home - Pet Care Network | Destination Pet</t>
@@ -70,7 +70,7 @@
     <t>live-webinar</t>
   </si>
   <si>
-    <t>2026-09-24T08:51:27.088Z</t>
+    <t>2026-09-24T12:08:45.757Z</t>
   </si>
   <si>
     <t>A Series of Webinars | Destination Pet</t>

--- a/tools/importer/reports/import-content-page.report.xlsx
+++ b/tools/importer/reports/import-content-page.report.xlsx
@@ -52,7 +52,7 @@
     <t>content-page</t>
   </si>
   <si>
-    <t>2026-09-24T12:08:41.569Z</t>
+    <t>2026-09-24T14:07:26.592Z</t>
   </si>
   <si>
     <t>Home - Pet Care Network | Destination Pet</t>
@@ -70,7 +70,7 @@
     <t>live-webinar</t>
   </si>
   <si>
-    <t>2026-09-24T12:08:45.757Z</t>
+    <t>2026-09-24T14:07:30.677Z</t>
   </si>
   <si>
     <t>A Series of Webinars | Destination Pet</t>
@@ -88,7 +88,7 @@
     <t>live-webinar/webinar-redirect</t>
   </si>
   <si>
-    <t>2026-09-24T08:14:45.556Z</t>
+    <t>2026-09-24T14:07:09.109Z</t>
   </si>
   <si>
     <t>Webinar Redirect - Destination Pet</t>

--- a/tools/importer/reports/import-content-page.report.xlsx
+++ b/tools/importer/reports/import-content-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="45">
   <si>
     <t>_reportFile</t>
   </si>
@@ -110,6 +110,42 @@
   </si>
   <si>
     <t>https://www.destinationpet.com/live-webinar/webinars-for-pet/</t>
+  </si>
+  <si>
+    <t>about-us/meet-the-team/business-development-leaders.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark","columns-comfortable-light","columns-comfortable-light","columns-comfortable-light","columns-comfortable-light"]</t>
+  </si>
+  <si>
+    <t>about-us/meet-the-team/business-development-leaders</t>
+  </si>
+  <si>
+    <t>2026-09-24T15:11:42.024Z</t>
+  </si>
+  <si>
+    <t>Business Development Leaders | Destination Pet</t>
+  </si>
+  <si>
+    <t>https://destinationpet.com/about-us/meet-the-team/business-development-leaders/</t>
+  </si>
+  <si>
+    <t>about-us/meet-the-team/leadership.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark","columns-comfortable-light","columns-comfortable-light","columns-comfortable-light","columns-comfortable-light","columns-comfortable-light","columns-comfortable-light","columns-comfortable-light"]</t>
+  </si>
+  <si>
+    <t>about-us/meet-the-team/leadership</t>
+  </si>
+  <si>
+    <t>2026-09-24T15:14:32.119Z</t>
+  </si>
+  <si>
+    <t>Leadership - Meet the team | Destination Pet</t>
+  </si>
+  <si>
+    <t>https://destinationpet.com/about-us/meet-the-team/leadership/</t>
   </si>
 </sst>
 </file>
@@ -498,15 +534,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="43" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="1" max="3" width="50" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="43" customWidth="1"/>
+    <col min="7" max="7" width="48" customWidth="1"/>
     <col min="8" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
@@ -638,6 +672,58 @@
       </c>
       <c r="H5" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-content-page.report.xlsx
+++ b/tools/importer/reports/import-content-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="51">
   <si>
     <t>_reportFile</t>
   </si>
@@ -77,6 +77,24 @@
   </si>
   <si>
     <t>https://www.destinationpet.com/live-webinar/</t>
+  </si>
+  <si>
+    <t>about-us/get-in-touch.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark","embed"]</t>
+  </si>
+  <si>
+    <t>about-us/get-in-touch</t>
+  </si>
+  <si>
+    <t>2026-09-24T15:46:54.898Z</t>
+  </si>
+  <si>
+    <t>Contact Us | Destination Pet, LLC</t>
+  </si>
+  <si>
+    <t>https://destinationpet.com/about-us/get-in-touch/</t>
   </si>
   <si>
     <t>live-webinar/webinar-redirect.report.json</t>
@@ -534,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -653,10 +671,10 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -665,21 +683,21 @@
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
         <v>35</v>
@@ -724,6 +742,32 @@
       </c>
       <c r="H7" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-content-page.report.xlsx
+++ b/tools/importer/reports/import-content-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="66">
   <si>
     <t>_reportFile</t>
   </si>
@@ -97,6 +97,21 @@
     <t>https://destinationpet.com/about-us/get-in-touch/</t>
   </si>
   <si>
+    <t>join-our-pack/find-a-veterinary-externship.report.json</t>
+  </si>
+  <si>
+    <t>join-our-pack/find-a-veterinary-externship</t>
+  </si>
+  <si>
+    <t>2026-09-24T16:03:21.285Z</t>
+  </si>
+  <si>
+    <t>Find a Veterinary Externship - Destination Pet</t>
+  </si>
+  <si>
+    <t>https://destinationpet.com/join-our-pack/find-a-veterinary-externship/</t>
+  </si>
+  <si>
     <t>live-webinar/webinar-redirect.report.json</t>
   </si>
   <si>
@@ -113,6 +128,36 @@
   </si>
   <si>
     <t>https://www.destinationpet.com/live-webinar/webinar-redirect/</t>
+  </si>
+  <si>
+    <t>live-webinar/webinar-registration.report.json</t>
+  </si>
+  <si>
+    <t>live-webinar/webinar-registration</t>
+  </si>
+  <si>
+    <t>2026-09-24T16:03:40.908Z</t>
+  </si>
+  <si>
+    <t>Webinar Registration - Destination Pet</t>
+  </si>
+  <si>
+    <t>https://destinationpet.com/live-webinar/webinar-registration/</t>
+  </si>
+  <si>
+    <t>live-webinar/webinar-viewing-previous.report.json</t>
+  </si>
+  <si>
+    <t>live-webinar/webinar-viewing-previous</t>
+  </si>
+  <si>
+    <t>2026-09-24T16:03:30.923Z</t>
+  </si>
+  <si>
+    <t>Webinar Viewing Previous - Destination Pet</t>
+  </si>
+  <si>
+    <t>https://destinationpet.com/live-webinar/webinar-viewing-previous/</t>
   </si>
   <si>
     <t>live-webinar/webinars-for-pet.report.json</t>
@@ -552,7 +597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -671,10 +716,10 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
         <v>29</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -683,21 +728,21 @@
         <v>12</v>
       </c>
       <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
         <v>31</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>32</v>
-      </c>
-      <c r="H5" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
         <v>34</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
       </c>
       <c r="C6" t="s">
         <v>35</v>
@@ -723,10 +768,10 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
         <v>40</v>
-      </c>
-      <c r="C7" t="s">
-        <v>41</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
@@ -735,24 +780,24 @@
         <v>12</v>
       </c>
       <c r="F7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" t="s">
         <v>42</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>43</v>
-      </c>
-      <c r="H7" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
         <v>45</v>
-      </c>
-      <c r="B8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" t="s">
-        <v>47</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
@@ -761,13 +806,91 @@
         <v>12</v>
       </c>
       <c r="F8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" t="s">
         <v>48</v>
       </c>
-      <c r="G8" t="s">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>49</v>
       </c>
-      <c r="H8" t="s">
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
         <v>50</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-content-page.report.xlsx
+++ b/tools/importer/reports/import-content-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="72">
   <si>
     <t>_reportFile</t>
   </si>
@@ -77,6 +77,24 @@
   </si>
   <si>
     <t>https://www.destinationpet.com/live-webinar/</t>
+  </si>
+  <si>
+    <t>sell-your-business.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark","cards","cards","quote","quote","embed"]</t>
+  </si>
+  <si>
+    <t>sell-your-business</t>
+  </si>
+  <si>
+    <t>2026-09-24T16:25:30.043Z</t>
+  </si>
+  <si>
+    <t>Sell Your Veterinary | Destination Pet</t>
+  </si>
+  <si>
+    <t>https://destinationpet.com/sell-your-business/</t>
   </si>
   <si>
     <t>about-us/get-in-touch.report.json</t>
@@ -597,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -716,10 +734,10 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -728,21 +746,21 @@
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
         <v>35</v>
@@ -768,10 +786,10 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
@@ -780,24 +798,24 @@
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
@@ -806,24 +824,24 @@
         <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
@@ -832,21 +850,21 @@
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
         <v>56</v>
@@ -891,6 +909,32 @@
       </c>
       <c r="H11" t="s">
         <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-content-page.report.xlsx
+++ b/tools/importer/reports/import-content-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="84">
   <si>
     <t>_reportFile</t>
   </si>
@@ -40,7 +40,7 @@
     <t>index.report.json</t>
   </si>
   <si>
-    <t>["hero-minimal-dark","columns-comfortable-light","cards","columns-minimal-light","quote","quote"]</t>
+    <t>["hero-minimal-dark","columns-comfortable-light","cards","cards","columns-minimal-light","quote","quote"]</t>
   </si>
   <si>
     <t>index</t>
@@ -52,7 +52,7 @@
     <t>content-page</t>
   </si>
   <si>
-    <t>2026-09-24T14:07:26.592Z</t>
+    <t>2026-09-25T08:05:44.881Z</t>
   </si>
   <si>
     <t>Home - Pet Care Network | Destination Pet</t>
@@ -70,7 +70,7 @@
     <t>live-webinar</t>
   </si>
   <si>
-    <t>2026-09-24T14:07:30.677Z</t>
+    <t>2026-09-25T08:02:35.749Z</t>
   </si>
   <si>
     <t>A Series of Webinars | Destination Pet</t>
@@ -88,7 +88,7 @@
     <t>sell-your-business</t>
   </si>
   <si>
-    <t>2026-09-24T16:25:30.043Z</t>
+    <t>2026-09-25T08:05:53.206Z</t>
   </si>
   <si>
     <t>Sell Your Veterinary | Destination Pet</t>
@@ -97,6 +97,24 @@
     <t>https://destinationpet.com/sell-your-business/</t>
   </si>
   <si>
+    <t>about-us/about.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark","columns-comfortable-light","columns-comfortable-light","columns-comfortable-light","columns-comfortable-light","columns-comfortable-light"]</t>
+  </si>
+  <si>
+    <t>about-us/about</t>
+  </si>
+  <si>
+    <t>2026-09-25T08:03:29.978Z</t>
+  </si>
+  <si>
+    <t>About Us | Destination Pet, LLC</t>
+  </si>
+  <si>
+    <t>https://destinationpet.com/about-us/about/</t>
+  </si>
+  <si>
     <t>about-us/get-in-touch.report.json</t>
   </si>
   <si>
@@ -106,7 +124,7 @@
     <t>about-us/get-in-touch</t>
   </si>
   <si>
-    <t>2026-09-24T15:46:54.898Z</t>
+    <t>2026-09-25T08:03:25.813Z</t>
   </si>
   <si>
     <t>Contact Us | Destination Pet, LLC</t>
@@ -121,7 +139,7 @@
     <t>join-our-pack/find-a-veterinary-externship</t>
   </si>
   <si>
-    <t>2026-09-24T16:03:21.285Z</t>
+    <t>2026-09-25T08:03:40.378Z</t>
   </si>
   <si>
     <t>Find a Veterinary Externship - Destination Pet</t>
@@ -130,6 +148,24 @@
     <t>https://destinationpet.com/join-our-pack/find-a-veterinary-externship/</t>
   </si>
   <si>
+    <t>join-our-pack/life-at-dp.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark","quote","video","accordion","accordion"]</t>
+  </si>
+  <si>
+    <t>join-our-pack/life-at-dp</t>
+  </si>
+  <si>
+    <t>2026-09-25T08:03:45.562Z</t>
+  </si>
+  <si>
+    <t>life at Destination Pet | Destination Pet</t>
+  </si>
+  <si>
+    <t>https://destinationpet.com/join-our-pack/life-at-dp/</t>
+  </si>
+  <si>
     <t>live-webinar/webinar-redirect.report.json</t>
   </si>
   <si>
@@ -139,7 +175,7 @@
     <t>live-webinar/webinar-redirect</t>
   </si>
   <si>
-    <t>2026-09-24T14:07:09.109Z</t>
+    <t>2026-09-25T08:02:41.623Z</t>
   </si>
   <si>
     <t>Webinar Redirect - Destination Pet</t>
@@ -154,7 +190,7 @@
     <t>live-webinar/webinar-registration</t>
   </si>
   <si>
-    <t>2026-09-24T16:03:40.908Z</t>
+    <t>2026-09-25T08:03:03.479Z</t>
   </si>
   <si>
     <t>Webinar Registration - Destination Pet</t>
@@ -169,7 +205,7 @@
     <t>live-webinar/webinar-viewing-previous</t>
   </si>
   <si>
-    <t>2026-09-24T16:03:30.923Z</t>
+    <t>2026-09-25T08:02:54.887Z</t>
   </si>
   <si>
     <t>Webinar Viewing Previous - Destination Pet</t>
@@ -184,7 +220,7 @@
     <t>live-webinar/webinars-for-pet</t>
   </si>
   <si>
-    <t>2026-09-24T08:14:49.609Z</t>
+    <t>2026-09-25T08:02:46.277Z</t>
   </si>
   <si>
     <t>Webinars for Pet - Destination Pet</t>
@@ -202,7 +238,7 @@
     <t>about-us/meet-the-team/business-development-leaders</t>
   </si>
   <si>
-    <t>2026-09-24T15:11:42.024Z</t>
+    <t>2026-09-25T08:03:09.150Z</t>
   </si>
   <si>
     <t>Business Development Leaders | Destination Pet</t>
@@ -220,7 +256,7 @@
     <t>about-us/meet-the-team/leadership</t>
   </si>
   <si>
-    <t>2026-09-24T15:14:32.119Z</t>
+    <t>2026-09-25T08:03:16.790Z</t>
   </si>
   <si>
     <t>Leadership - Meet the team | Destination Pet</t>
@@ -615,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -760,10 +796,10 @@
         <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
@@ -772,21 +808,21 @@
         <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
         <v>41</v>
@@ -812,10 +848,10 @@
         <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
@@ -824,24 +860,24 @@
         <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
@@ -850,24 +886,24 @@
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
@@ -876,24 +912,24 @@
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -902,21 +938,21 @@
         <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
         <v>68</v>
@@ -935,6 +971,58 @@
       </c>
       <c r="H12" t="s">
         <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" t="s">
+        <v>75</v>
+      </c>
+      <c r="G13" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-content-page.report.xlsx
+++ b/tools/importer/reports/import-content-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="96">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,7 +52,7 @@
     <t>content-page</t>
   </si>
   <si>
-    <t>2026-09-25T08:05:44.881Z</t>
+    <t>2026-09-25T09:23:16.408Z</t>
   </si>
   <si>
     <t>Home - Pet Care Network | Destination Pet</t>
@@ -70,7 +70,7 @@
     <t>live-webinar</t>
   </si>
   <si>
-    <t>2026-09-25T08:02:35.749Z</t>
+    <t>2026-09-25T09:23:20.477Z</t>
   </si>
   <si>
     <t>A Series of Webinars | Destination Pet</t>
@@ -88,7 +88,7 @@
     <t>sell-your-business</t>
   </si>
   <si>
-    <t>2026-09-25T08:05:53.206Z</t>
+    <t>2026-09-25T09:22:59.497Z</t>
   </si>
   <si>
     <t>Sell Your Veterinary | Destination Pet</t>
@@ -106,7 +106,7 @@
     <t>about-us/about</t>
   </si>
   <si>
-    <t>2026-09-25T08:03:29.978Z</t>
+    <t>2026-09-25T09:21:59.592Z</t>
   </si>
   <si>
     <t>About Us | Destination Pet, LLC</t>
@@ -124,7 +124,7 @@
     <t>about-us/get-in-touch</t>
   </si>
   <si>
-    <t>2026-09-25T08:03:25.813Z</t>
+    <t>2026-09-25T09:22:07.953Z</t>
   </si>
   <si>
     <t>Contact Us | Destination Pet, LLC</t>
@@ -139,7 +139,7 @@
     <t>join-our-pack/find-a-veterinary-externship</t>
   </si>
   <si>
-    <t>2026-09-25T08:03:40.378Z</t>
+    <t>2026-09-25T09:22:29.117Z</t>
   </si>
   <si>
     <t>Find a Veterinary Externship - Destination Pet</t>
@@ -157,7 +157,7 @@
     <t>join-our-pack/life-at-dp</t>
   </si>
   <si>
-    <t>2026-09-25T08:03:45.562Z</t>
+    <t>2026-09-25T09:22:33.940Z</t>
   </si>
   <si>
     <t>life at Destination Pet | Destination Pet</t>
@@ -175,7 +175,7 @@
     <t>live-webinar/webinar-redirect</t>
   </si>
   <si>
-    <t>2026-09-25T08:02:41.623Z</t>
+    <t>2026-09-25T09:23:25.203Z</t>
   </si>
   <si>
     <t>Webinar Redirect - Destination Pet</t>
@@ -190,7 +190,7 @@
     <t>live-webinar/webinar-registration</t>
   </si>
   <si>
-    <t>2026-09-25T08:03:03.479Z</t>
+    <t>2026-09-25T09:22:42.423Z</t>
   </si>
   <si>
     <t>Webinar Registration - Destination Pet</t>
@@ -205,7 +205,7 @@
     <t>live-webinar/webinar-viewing-previous</t>
   </si>
   <si>
-    <t>2026-09-25T08:02:54.887Z</t>
+    <t>2026-09-25T09:22:49.302Z</t>
   </si>
   <si>
     <t>Webinar Viewing Previous - Destination Pet</t>
@@ -220,7 +220,7 @@
     <t>live-webinar/webinars-for-pet</t>
   </si>
   <si>
-    <t>2026-09-25T08:02:46.277Z</t>
+    <t>2026-09-25T09:23:32.140Z</t>
   </si>
   <si>
     <t>Webinars for Pet - Destination Pet</t>
@@ -229,6 +229,42 @@
     <t>https://www.destinationpet.com/live-webinar/webinars-for-pet/</t>
   </si>
   <si>
+    <t>sell-your-business/sell-your-pet-resort.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark","carousel","carousel","cards","quote","quote","quote","accordion"]</t>
+  </si>
+  <si>
+    <t>sell-your-business/sell-your-pet-resort</t>
+  </si>
+  <si>
+    <t>2026-09-25T09:23:07.097Z</t>
+  </si>
+  <si>
+    <t>Sell Your Pet Resort - Destination Pet</t>
+  </si>
+  <si>
+    <t>https://destinationpet.com/sell-your-business/sell-your-pet-resort/</t>
+  </si>
+  <si>
+    <t>sell-your-business/sell-your-veterinary-practice.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark","carousel","carousel","cards","cards","cards","quote","quote","accordion"]</t>
+  </si>
+  <si>
+    <t>sell-your-business/sell-your-veterinary-practice</t>
+  </si>
+  <si>
+    <t>2026-09-25T09:23:11.896Z</t>
+  </si>
+  <si>
+    <t>Sell your veterinary practice | Destination Pet</t>
+  </si>
+  <si>
+    <t>https://destinationpet.com/sell-your-business/sell-your-veterinary-practice/</t>
+  </si>
+  <si>
     <t>about-us/meet-the-team/business-development-leaders.report.json</t>
   </si>
   <si>
@@ -238,7 +274,7 @@
     <t>about-us/meet-the-team/business-development-leaders</t>
   </si>
   <si>
-    <t>2026-09-25T08:03:09.150Z</t>
+    <t>2026-09-25T09:22:15.051Z</t>
   </si>
   <si>
     <t>Business Development Leaders | Destination Pet</t>
@@ -256,7 +292,7 @@
     <t>about-us/meet-the-team/leadership</t>
   </si>
   <si>
-    <t>2026-09-25T08:03:16.790Z</t>
+    <t>2026-09-25T09:22:21.908Z</t>
   </si>
   <si>
     <t>Leadership - Meet the team | Destination Pet</t>
@@ -651,13 +687,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="48" customWidth="1"/>
+    <col min="7" max="7" width="49" customWidth="1"/>
     <col min="8" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1025,6 +1061,58 @@
         <v>83</v>
       </c>
     </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" t="s">
+        <v>88</v>
+      </c>
+      <c r="H15" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
+        <v>93</v>
+      </c>
+      <c r="G16" t="s">
+        <v>94</v>
+      </c>
+      <c r="H16" t="s">
+        <v>95</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tools/importer/reports/import-content-page.report.xlsx
+++ b/tools/importer/reports/import-content-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="102">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,7 +52,7 @@
     <t>content-page</t>
   </si>
   <si>
-    <t>2026-09-25T09:23:16.408Z</t>
+    <t>2026-09-25T10:39:37.298Z</t>
   </si>
   <si>
     <t>Home - Pet Care Network | Destination Pet</t>
@@ -70,7 +70,7 @@
     <t>live-webinar</t>
   </si>
   <si>
-    <t>2026-09-25T09:23:20.477Z</t>
+    <t>2026-09-25T10:39:42.384Z</t>
   </si>
   <si>
     <t>A Series of Webinars | Destination Pet</t>
@@ -79,6 +79,24 @@
     <t>https://www.destinationpet.com/live-webinar/</t>
   </si>
   <si>
+    <t>our-locations.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark","cards-logos","cards-logos","cards-logos","cards-logos","cards-logos","cards-logos","cards-logos","cards-logos","cards-logos","cards-logos","cards-logos","cards-logos","cards-logos","cards-logos","cards-logos","cards-logos","cards-logos","cards-logos","cards-logos","cards-logos","cards-logos","cards-logos","cards-logos","cards-logos","cards-logos","cards-logos","cards-logos","cards-logos","cards-logos","cards-logos","cards-logos","columns-link-list","columns-minimal-light","columns-minimal-light","columns-minimal-light","columns-minimal-light","columns-minimal-light","columns-minimal-light","columns-minimal-light","columns-minimal-light"]</t>
+  </si>
+  <si>
+    <t>our-locations</t>
+  </si>
+  <si>
+    <t>2026-09-25T11:16:28.595Z</t>
+  </si>
+  <si>
+    <t>Our Locations | Destination Pet</t>
+  </si>
+  <si>
+    <t>https://destinationpet.com/our-locations/</t>
+  </si>
+  <si>
     <t>sell-your-business.report.json</t>
   </si>
   <si>
@@ -88,7 +106,7 @@
     <t>sell-your-business</t>
   </si>
   <si>
-    <t>2026-09-25T09:22:59.497Z</t>
+    <t>2026-09-25T10:39:20.617Z</t>
   </si>
   <si>
     <t>Sell Your Veterinary | Destination Pet</t>
@@ -106,7 +124,7 @@
     <t>about-us/about</t>
   </si>
   <si>
-    <t>2026-09-25T09:21:59.592Z</t>
+    <t>2026-09-25T10:38:10.803Z</t>
   </si>
   <si>
     <t>About Us | Destination Pet, LLC</t>
@@ -124,7 +142,7 @@
     <t>about-us/get-in-touch</t>
   </si>
   <si>
-    <t>2026-09-25T09:22:07.953Z</t>
+    <t>2026-09-25T10:38:17.613Z</t>
   </si>
   <si>
     <t>Contact Us | Destination Pet, LLC</t>
@@ -139,7 +157,7 @@
     <t>join-our-pack/find-a-veterinary-externship</t>
   </si>
   <si>
-    <t>2026-09-25T09:22:29.117Z</t>
+    <t>2026-09-25T10:38:40.926Z</t>
   </si>
   <si>
     <t>Find a Veterinary Externship - Destination Pet</t>
@@ -157,7 +175,7 @@
     <t>join-our-pack/life-at-dp</t>
   </si>
   <si>
-    <t>2026-09-25T09:22:33.940Z</t>
+    <t>2026-09-25T10:38:46.361Z</t>
   </si>
   <si>
     <t>life at Destination Pet | Destination Pet</t>
@@ -175,7 +193,7 @@
     <t>live-webinar/webinar-redirect</t>
   </si>
   <si>
-    <t>2026-09-25T09:23:25.203Z</t>
+    <t>2026-09-25T10:39:48.868Z</t>
   </si>
   <si>
     <t>Webinar Redirect - Destination Pet</t>
@@ -190,7 +208,7 @@
     <t>live-webinar/webinar-registration</t>
   </si>
   <si>
-    <t>2026-09-25T09:22:42.423Z</t>
+    <t>2026-09-25T10:38:55.802Z</t>
   </si>
   <si>
     <t>Webinar Registration - Destination Pet</t>
@@ -205,7 +223,7 @@
     <t>live-webinar/webinar-viewing-previous</t>
   </si>
   <si>
-    <t>2026-09-25T09:22:49.302Z</t>
+    <t>2026-09-25T10:39:04.893Z</t>
   </si>
   <si>
     <t>Webinar Viewing Previous - Destination Pet</t>
@@ -220,7 +238,7 @@
     <t>live-webinar/webinars-for-pet</t>
   </si>
   <si>
-    <t>2026-09-25T09:23:32.140Z</t>
+    <t>2026-09-25T10:39:55.021Z</t>
   </si>
   <si>
     <t>Webinars for Pet - Destination Pet</t>
@@ -238,7 +256,7 @@
     <t>sell-your-business/sell-your-pet-resort</t>
   </si>
   <si>
-    <t>2026-09-25T09:23:07.097Z</t>
+    <t>2026-09-25T10:39:25.961Z</t>
   </si>
   <si>
     <t>Sell Your Pet Resort - Destination Pet</t>
@@ -256,7 +274,7 @@
     <t>sell-your-business/sell-your-veterinary-practice</t>
   </si>
   <si>
-    <t>2026-09-25T09:23:11.896Z</t>
+    <t>2026-09-25T10:39:30.616Z</t>
   </si>
   <si>
     <t>Sell your veterinary practice | Destination Pet</t>
@@ -274,7 +292,7 @@
     <t>about-us/meet-the-team/business-development-leaders</t>
   </si>
   <si>
-    <t>2026-09-25T09:22:15.051Z</t>
+    <t>2026-09-25T10:38:24.705Z</t>
   </si>
   <si>
     <t>Business Development Leaders | Destination Pet</t>
@@ -292,7 +310,7 @@
     <t>about-us/meet-the-team/leadership</t>
   </si>
   <si>
-    <t>2026-09-25T09:22:21.908Z</t>
+    <t>2026-09-25T10:38:29.476Z</t>
   </si>
   <si>
     <t>Leadership - Meet the team | Destination Pet</t>
@@ -687,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -858,10 +876,10 @@
         <v>40</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
@@ -870,21 +888,21 @@
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
         <v>47</v>
@@ -936,10 +954,10 @@
         <v>57</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
@@ -948,24 +966,24 @@
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -974,24 +992,24 @@
         <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
@@ -1000,21 +1018,21 @@
         <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C13" t="s">
         <v>74</v>
@@ -1111,6 +1129,32 @@
       </c>
       <c r="H16" t="s">
         <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" t="s">
+        <v>99</v>
+      </c>
+      <c r="G17" t="s">
+        <v>100</v>
+      </c>
+      <c r="H17" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-content-page.report.xlsx
+++ b/tools/importer/reports/import-content-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="123">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,7 +52,7 @@
     <t>content-page</t>
   </si>
   <si>
-    <t>2026-09-25T10:39:37.298Z</t>
+    <t>2026-09-25T12:07:45.763Z</t>
   </si>
   <si>
     <t>Home - Pet Care Network | Destination Pet</t>
@@ -70,7 +70,7 @@
     <t>live-webinar</t>
   </si>
   <si>
-    <t>2026-09-25T10:39:42.384Z</t>
+    <t>2026-09-25T12:07:53.740Z</t>
   </si>
   <si>
     <t>A Series of Webinars | Destination Pet</t>
@@ -88,7 +88,7 @@
     <t>our-locations</t>
   </si>
   <si>
-    <t>2026-09-25T11:16:28.595Z</t>
+    <t>2026-09-25T12:07:19.869Z</t>
   </si>
   <si>
     <t>Our Locations | Destination Pet</t>
@@ -97,6 +97,24 @@
     <t>https://destinationpet.com/our-locations/</t>
   </si>
   <si>
+    <t>privacy-policy.report.json</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>privacy-policy</t>
+  </si>
+  <si>
+    <t>2026-09-25T12:08:13.438Z</t>
+  </si>
+  <si>
+    <t>Privacy Policy | Destination Pet</t>
+  </si>
+  <si>
+    <t>https://destinationpet.com/privacy-policy/</t>
+  </si>
+  <si>
     <t>sell-your-business.report.json</t>
   </si>
   <si>
@@ -106,7 +124,7 @@
     <t>sell-your-business</t>
   </si>
   <si>
-    <t>2026-09-25T10:39:20.617Z</t>
+    <t>2026-09-25T12:07:28.188Z</t>
   </si>
   <si>
     <t>Sell Your Veterinary | Destination Pet</t>
@@ -115,6 +133,21 @@
     <t>https://destinationpet.com/sell-your-business/</t>
   </si>
   <si>
+    <t>terms-and-conditions.report.json</t>
+  </si>
+  <si>
+    <t>terms-and-conditions</t>
+  </si>
+  <si>
+    <t>2026-09-25T12:08:19.034Z</t>
+  </si>
+  <si>
+    <t>Terms and Conditions | Destination Pet</t>
+  </si>
+  <si>
+    <t>https://destinationpet.com/terms-and-conditions/</t>
+  </si>
+  <si>
     <t>about-us/about.report.json</t>
   </si>
   <si>
@@ -124,7 +157,7 @@
     <t>about-us/about</t>
   </si>
   <si>
-    <t>2026-09-25T10:38:10.803Z</t>
+    <t>2026-09-25T12:06:18.002Z</t>
   </si>
   <si>
     <t>About Us | Destination Pet, LLC</t>
@@ -133,6 +166,21 @@
     <t>https://destinationpet.com/about-us/about/</t>
   </si>
   <si>
+    <t>about-us/ccpa-request.report.json</t>
+  </si>
+  <si>
+    <t>about-us/ccpa-request</t>
+  </si>
+  <si>
+    <t>2026-09-25T12:08:26.308Z</t>
+  </si>
+  <si>
+    <t>CCPA Request - Destination Pet</t>
+  </si>
+  <si>
+    <t>https://destinationpet.com/about-us/ccpa-request/</t>
+  </si>
+  <si>
     <t>about-us/get-in-touch.report.json</t>
   </si>
   <si>
@@ -142,7 +190,7 @@
     <t>about-us/get-in-touch</t>
   </si>
   <si>
-    <t>2026-09-25T10:38:17.613Z</t>
+    <t>2026-09-25T12:06:27.805Z</t>
   </si>
   <si>
     <t>Contact Us | Destination Pet, LLC</t>
@@ -151,13 +199,28 @@
     <t>https://destinationpet.com/about-us/get-in-touch/</t>
   </si>
   <si>
+    <t>about-us/tradeshows-events.report.json</t>
+  </si>
+  <si>
+    <t>about-us/tradeshows-events</t>
+  </si>
+  <si>
+    <t>2026-09-25T12:08:31.362Z</t>
+  </si>
+  <si>
+    <t>Tradeshows - Events - Destination Pet</t>
+  </si>
+  <si>
+    <t>https://destinationpet.com/about-us/tradeshows-events/</t>
+  </si>
+  <si>
     <t>join-our-pack/find-a-veterinary-externship.report.json</t>
   </si>
   <si>
     <t>join-our-pack/find-a-veterinary-externship</t>
   </si>
   <si>
-    <t>2026-09-25T10:38:40.926Z</t>
+    <t>2026-09-25T12:06:52.038Z</t>
   </si>
   <si>
     <t>Find a Veterinary Externship - Destination Pet</t>
@@ -175,7 +238,7 @@
     <t>join-our-pack/life-at-dp</t>
   </si>
   <si>
-    <t>2026-09-25T10:38:46.361Z</t>
+    <t>2026-09-25T12:06:57.570Z</t>
   </si>
   <si>
     <t>life at Destination Pet | Destination Pet</t>
@@ -193,7 +256,7 @@
     <t>live-webinar/webinar-redirect</t>
   </si>
   <si>
-    <t>2026-09-25T10:39:48.868Z</t>
+    <t>2026-09-25T12:08:00.774Z</t>
   </si>
   <si>
     <t>Webinar Redirect - Destination Pet</t>
@@ -208,7 +271,7 @@
     <t>live-webinar/webinar-registration</t>
   </si>
   <si>
-    <t>2026-09-25T10:38:55.802Z</t>
+    <t>2026-09-25T12:07:05.155Z</t>
   </si>
   <si>
     <t>Webinar Registration - Destination Pet</t>
@@ -223,7 +286,7 @@
     <t>live-webinar/webinar-viewing-previous</t>
   </si>
   <si>
-    <t>2026-09-25T10:39:04.893Z</t>
+    <t>2026-09-25T12:07:13.226Z</t>
   </si>
   <si>
     <t>Webinar Viewing Previous - Destination Pet</t>
@@ -238,7 +301,7 @@
     <t>live-webinar/webinars-for-pet</t>
   </si>
   <si>
-    <t>2026-09-25T10:39:55.021Z</t>
+    <t>2026-09-25T12:08:06.098Z</t>
   </si>
   <si>
     <t>Webinars for Pet - Destination Pet</t>
@@ -256,7 +319,7 @@
     <t>sell-your-business/sell-your-pet-resort</t>
   </si>
   <si>
-    <t>2026-09-25T10:39:25.961Z</t>
+    <t>2026-09-25T12:07:34.711Z</t>
   </si>
   <si>
     <t>Sell Your Pet Resort - Destination Pet</t>
@@ -274,7 +337,7 @@
     <t>sell-your-business/sell-your-veterinary-practice</t>
   </si>
   <si>
-    <t>2026-09-25T10:39:30.616Z</t>
+    <t>2026-09-25T12:07:40.895Z</t>
   </si>
   <si>
     <t>Sell your veterinary practice | Destination Pet</t>
@@ -292,7 +355,7 @@
     <t>about-us/meet-the-team/business-development-leaders</t>
   </si>
   <si>
-    <t>2026-09-25T10:38:24.705Z</t>
+    <t>2026-09-25T12:06:35.199Z</t>
   </si>
   <si>
     <t>Business Development Leaders | Destination Pet</t>
@@ -310,7 +373,7 @@
     <t>about-us/meet-the-team/leadership</t>
   </si>
   <si>
-    <t>2026-09-25T10:38:29.476Z</t>
+    <t>2026-09-25T12:06:42.174Z</t>
   </si>
   <si>
     <t>Leadership - Meet the team | Destination Pet</t>
@@ -705,7 +768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -876,33 +939,33 @@
         <v>40</v>
       </c>
       <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
         <v>41</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
         <v>42</v>
       </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>44</v>
-      </c>
-      <c r="H7" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
         <v>46</v>
-      </c>
-      <c r="B8" t="s">
-        <v>41</v>
       </c>
       <c r="C8" t="s">
         <v>47</v>
@@ -928,111 +991,111 @@
         <v>51</v>
       </c>
       <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
         <v>52</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
         <v>53</v>
       </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>54</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>55</v>
-      </c>
-      <c r="H9" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" t="s">
         <v>57</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>58</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
         <v>59</v>
       </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>60</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>61</v>
-      </c>
-      <c r="H10" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
         <v>63</v>
       </c>
-      <c r="B11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
         <v>64</v>
       </c>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>65</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>66</v>
-      </c>
-      <c r="H11" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" t="s">
         <v>68</v>
       </c>
-      <c r="B12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" t="s">
         <v>69</v>
       </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>70</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>71</v>
-      </c>
-      <c r="H12" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" t="s">
         <v>73</v>
-      </c>
-      <c r="B13" t="s">
-        <v>58</v>
       </c>
       <c r="C13" t="s">
         <v>74</v>
@@ -1084,77 +1147,181 @@
         <v>84</v>
       </c>
       <c r="B15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" t="s">
         <v>85</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
         <v>86</v>
       </c>
-      <c r="D15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>87</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>88</v>
-      </c>
-      <c r="H15" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" t="s">
         <v>90</v>
       </c>
-      <c r="B16" t="s">
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
         <v>91</v>
       </c>
-      <c r="C16" t="s">
+      <c r="G16" t="s">
         <v>92</v>
       </c>
-      <c r="D16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="H16" t="s">
         <v>93</v>
-      </c>
-      <c r="G16" t="s">
-        <v>94</v>
-      </c>
-      <c r="H16" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" t="s">
         <v>96</v>
       </c>
-      <c r="B17" t="s">
+      <c r="G17" t="s">
         <v>97</v>
       </c>
-      <c r="C17" t="s">
+      <c r="H17" t="s">
         <v>98</v>
       </c>
-      <c r="D17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" t="s">
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>99</v>
       </c>
-      <c r="G17" t="s">
+      <c r="B18" t="s">
         <v>100</v>
       </c>
-      <c r="H17" t="s">
+      <c r="C18" t="s">
         <v>101</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" t="s">
+        <v>102</v>
+      </c>
+      <c r="G18" t="s">
+        <v>103</v>
+      </c>
+      <c r="H18" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" t="s">
+        <v>108</v>
+      </c>
+      <c r="G19" t="s">
+        <v>109</v>
+      </c>
+      <c r="H19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>111</v>
+      </c>
+      <c r="B20" t="s">
+        <v>112</v>
+      </c>
+      <c r="C20" t="s">
+        <v>113</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" t="s">
+        <v>114</v>
+      </c>
+      <c r="G20" t="s">
+        <v>115</v>
+      </c>
+      <c r="H20" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C21" t="s">
+        <v>119</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" t="s">
+        <v>120</v>
+      </c>
+      <c r="G21" t="s">
+        <v>121</v>
+      </c>
+      <c r="H21" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-content-page.report.xlsx
+++ b/tools/importer/reports/import-content-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="129">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,7 +52,7 @@
     <t>content-page</t>
   </si>
   <si>
-    <t>2026-09-25T12:07:45.763Z</t>
+    <t>2026-09-25T15:15:10.164Z</t>
   </si>
   <si>
     <t>Home - Pet Care Network | Destination Pet</t>
@@ -70,7 +70,7 @@
     <t>live-webinar</t>
   </si>
   <si>
-    <t>2026-09-25T12:07:53.740Z</t>
+    <t>2026-09-25T15:15:18.471Z</t>
   </si>
   <si>
     <t>A Series of Webinars | Destination Pet</t>
@@ -88,7 +88,7 @@
     <t>our-locations</t>
   </si>
   <si>
-    <t>2026-09-25T12:07:19.869Z</t>
+    <t>2026-09-25T15:14:44.901Z</t>
   </si>
   <si>
     <t>Our Locations | Destination Pet</t>
@@ -106,7 +106,7 @@
     <t>privacy-policy</t>
   </si>
   <si>
-    <t>2026-09-25T12:08:13.438Z</t>
+    <t>2026-09-25T15:15:37.567Z</t>
   </si>
   <si>
     <t>Privacy Policy | Destination Pet</t>
@@ -124,7 +124,7 @@
     <t>sell-your-business</t>
   </si>
   <si>
-    <t>2026-09-25T12:07:28.188Z</t>
+    <t>2026-09-25T15:14:51.341Z</t>
   </si>
   <si>
     <t>Sell Your Veterinary | Destination Pet</t>
@@ -139,7 +139,7 @@
     <t>terms-and-conditions</t>
   </si>
   <si>
-    <t>2026-09-25T12:08:19.034Z</t>
+    <t>2026-09-25T15:15:43.582Z</t>
   </si>
   <si>
     <t>Terms and Conditions | Destination Pet</t>
@@ -157,7 +157,7 @@
     <t>about-us/about</t>
   </si>
   <si>
-    <t>2026-09-25T12:06:18.002Z</t>
+    <t>2026-09-25T15:13:43.988Z</t>
   </si>
   <si>
     <t>About Us | Destination Pet, LLC</t>
@@ -172,7 +172,7 @@
     <t>about-us/ccpa-request</t>
   </si>
   <si>
-    <t>2026-09-25T12:08:26.308Z</t>
+    <t>2026-09-25T15:15:49.328Z</t>
   </si>
   <si>
     <t>CCPA Request - Destination Pet</t>
@@ -181,6 +181,24 @@
     <t>https://destinationpet.com/about-us/ccpa-request/</t>
   </si>
   <si>
+    <t>about-us/destination-pet-foundation.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark","carousel","columns-comfortable-light"]</t>
+  </si>
+  <si>
+    <t>about-us/destination-pet-foundation</t>
+  </si>
+  <si>
+    <t>2026-09-25T15:16:01.363Z</t>
+  </si>
+  <si>
+    <t>Destination Pet Foundation - Destination Pet</t>
+  </si>
+  <si>
+    <t>https://www.destinationpet.com/about-us/destination-pet-foundation/</t>
+  </si>
+  <si>
     <t>about-us/get-in-touch.report.json</t>
   </si>
   <si>
@@ -190,7 +208,7 @@
     <t>about-us/get-in-touch</t>
   </si>
   <si>
-    <t>2026-09-25T12:06:27.805Z</t>
+    <t>2026-09-25T15:13:54.534Z</t>
   </si>
   <si>
     <t>Contact Us | Destination Pet, LLC</t>
@@ -205,7 +223,7 @@
     <t>about-us/tradeshows-events</t>
   </si>
   <si>
-    <t>2026-09-25T12:08:31.362Z</t>
+    <t>2026-09-25T15:15:55.436Z</t>
   </si>
   <si>
     <t>Tradeshows - Events - Destination Pet</t>
@@ -220,7 +238,7 @@
     <t>join-our-pack/find-a-veterinary-externship</t>
   </si>
   <si>
-    <t>2026-09-25T12:06:52.038Z</t>
+    <t>2026-09-25T15:14:14.404Z</t>
   </si>
   <si>
     <t>Find a Veterinary Externship - Destination Pet</t>
@@ -238,7 +256,7 @@
     <t>join-our-pack/life-at-dp</t>
   </si>
   <si>
-    <t>2026-09-25T12:06:57.570Z</t>
+    <t>2026-09-25T15:14:19.974Z</t>
   </si>
   <si>
     <t>life at Destination Pet | Destination Pet</t>
@@ -256,7 +274,7 @@
     <t>live-webinar/webinar-redirect</t>
   </si>
   <si>
-    <t>2026-09-25T12:08:00.774Z</t>
+    <t>2026-09-25T15:15:24.512Z</t>
   </si>
   <si>
     <t>Webinar Redirect - Destination Pet</t>
@@ -271,7 +289,7 @@
     <t>live-webinar/webinar-registration</t>
   </si>
   <si>
-    <t>2026-09-25T12:07:05.155Z</t>
+    <t>2026-09-25T15:14:28.444Z</t>
   </si>
   <si>
     <t>Webinar Registration - Destination Pet</t>
@@ -286,7 +304,7 @@
     <t>live-webinar/webinar-viewing-previous</t>
   </si>
   <si>
-    <t>2026-09-25T12:07:13.226Z</t>
+    <t>2026-09-25T15:14:37.215Z</t>
   </si>
   <si>
     <t>Webinar Viewing Previous - Destination Pet</t>
@@ -301,7 +319,7 @@
     <t>live-webinar/webinars-for-pet</t>
   </si>
   <si>
-    <t>2026-09-25T12:08:06.098Z</t>
+    <t>2026-09-25T15:15:31.003Z</t>
   </si>
   <si>
     <t>Webinars for Pet - Destination Pet</t>
@@ -319,7 +337,7 @@
     <t>sell-your-business/sell-your-pet-resort</t>
   </si>
   <si>
-    <t>2026-09-25T12:07:34.711Z</t>
+    <t>2026-09-25T15:14:58.099Z</t>
   </si>
   <si>
     <t>Sell Your Pet Resort - Destination Pet</t>
@@ -337,7 +355,7 @@
     <t>sell-your-business/sell-your-veterinary-practice</t>
   </si>
   <si>
-    <t>2026-09-25T12:07:40.895Z</t>
+    <t>2026-09-25T15:15:04.234Z</t>
   </si>
   <si>
     <t>Sell your veterinary practice | Destination Pet</t>
@@ -355,7 +373,7 @@
     <t>about-us/meet-the-team/business-development-leaders</t>
   </si>
   <si>
-    <t>2026-09-25T12:06:35.199Z</t>
+    <t>2026-09-25T15:14:01.038Z</t>
   </si>
   <si>
     <t>Business Development Leaders | Destination Pet</t>
@@ -373,7 +391,7 @@
     <t>about-us/meet-the-team/leadership</t>
   </si>
   <si>
-    <t>2026-09-25T12:06:42.174Z</t>
+    <t>2026-09-25T15:14:06.698Z</t>
   </si>
   <si>
     <t>Leadership - Meet the team | Destination Pet</t>
@@ -768,7 +786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -1043,10 +1061,10 @@
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -1055,24 +1073,24 @@
         <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
@@ -1081,21 +1099,21 @@
         <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
         <v>74</v>
@@ -1147,10 +1165,10 @@
         <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
@@ -1159,24 +1177,24 @@
         <v>12</v>
       </c>
       <c r="F15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
@@ -1185,24 +1203,24 @@
         <v>12</v>
       </c>
       <c r="F16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
@@ -1211,21 +1229,21 @@
         <v>12</v>
       </c>
       <c r="F17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B18" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
         <v>101</v>
@@ -1322,6 +1340,32 @@
       </c>
       <c r="H21" t="s">
         <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B22" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" t="s">
+        <v>125</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" t="s">
+        <v>126</v>
+      </c>
+      <c r="G22" t="s">
+        <v>127</v>
+      </c>
+      <c r="H22" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
